--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Redshift, BigQuery, Data Lake, CI/CD, Terraform, Git, Snowflake</t>
+          <t>RAG, Cortex, S3, Kinesis, Docker, Git, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Melbourne, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, S3, Redshift, Data Lake, Snowflake, Redshift, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aac28cd79dafb61</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Engineer, AI Platform - Business Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zenith Insurance Company</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, PyTorch, XGBoost, FastAPI, Git</t>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a82f2b1c121b82f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a783290fd5509d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=5464981dff92414f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Engineer - Workplace Services Engineering</t>
+          <t>Platform Engineer - PAM Core</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Kinesis, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8100e5877860b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8affe155552045a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Scientist - Agentic AI &amp; Decision Intelligence</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cortex, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, Tableau</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=45a35f0784ab52b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist, Commercial Analytics</t>
+          <t>Senior Data Analyst- Business Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343be0a011ed23f4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa67e54d436bc01b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MarketBridge</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225e04a822997236</t>
+          <t>https://www.indeed.com/viewjob?jk=30de852eaf2dbcd8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Synapse, Snowflake, Databricks, Redshift, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data, Analytics and AI Platform Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, EC2, Athena, Git, Snowflake, Databricks, PySpark, MySQL, Python, SQL</t>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,602 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Blue Shield of California</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Python Vue Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rev Agency</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Westbury, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LangChain, S3, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=998830b6711c09f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer - Generative AI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26df1a544eb82911</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Fullstack Engineer - US</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cyera</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, FastAPI, Docker, CI/CD, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8be9543103312b81</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Perception Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f7b37c4490f2e69</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer - Full Stack, Information Technology</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ServiceLink</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4262c033bb0929f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cologix, Inc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac9f634fa04ee03d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>insitro.com</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>South San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22b8d3007b62ff4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Summer Intern, Embedded Machine Learning Engineer (AI/ML)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cirrus Logic</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Cortex, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63f8fba26a73471a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Analyst - Kiewit Infrastructure Engineers</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kiewit Corporation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Lone Tree, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9af49541c38e843d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Summer Intern, Embedded Machine Learning Engineer (AI/ML)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cirrus Logic</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Cortex, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58a970a2214897ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Product Development AI Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Gates Corporation</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af53675c5fc1d79d</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HealthEquity Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, AKS, Jenkins, Git, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b0e4ecf65282d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6c01868d7f186a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer (Data and Analytics Cloud Engineer)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Information Technology Senior Management Forum</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02b2daf69bfa211e</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Continued</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be8eb3d7fca68368</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr Data Analyst</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>University of Pittsburgh</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=36350d677bd0b22a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5fe084cebe89c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Kinesis, Docker, Git, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, BigQuery, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,357 +496,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Research Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Oak Ridge National Laboratory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, S3, MLflow, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcd461a7083269</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Redshift, Data Lake, Snowflake, Redshift, MySQL, Python, SQL</t>
+          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI Platform - Business Technology</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a783290fd5509d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GE HealthCare</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5464981dff92414f</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Platform Engineer - PAM Core</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kinesis, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8affe155552045a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Agentic AI &amp; Decision Intelligence</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Wellesley, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Snowflake, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45a35f0784ab52b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst- Business Analytics &amp; AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mattel, Inc.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa67e54d436bc01b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30de852eaf2dbcd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GRP Solutions</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Texas City, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5fe084cebe89c0</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Senior ML Engineer, Generative AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, BigQuery, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, XGBoost, S3, EC2, Glue, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Research Software Engineer</t>
+          <t>AI Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Flexday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcd461a7083269</t>
+          <t>https://www.indeed.com/viewjob?jk=d5323b9effb948f0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior AI Engineer, Global Banking &amp; Markets, RIA Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Pinecone, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=bc401ce0ff1b7af4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,227 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Kafka, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineering, Enterprise IAM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f237f0aade6c7a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Founding Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e4528f3f265ee0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce378543f6aedb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83a1d5c6d0344680</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; AI Engineer - Drilling Services</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Weatherford</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4cef0d3964a633a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supply Chain AI Enablement Intern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Gas and Electric</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b280b1bc6faa783d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Generative AI</t>
+          <t>Software Fullstack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>BirdEye Inc India</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, XGBoost, S3, EC2, Glue, Docker, Kubernetes</t>
+          <t>S3, EC2, Docker, Kubernetes, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8a8e0919415865</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer, Agentic AI</t>
+          <t>Software Engineer - Machine Learning</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flexday</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5323b9effb948f0</t>
+          <t>https://www.indeed.com/viewjob?jk=038eede1aae64fff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Global Banking &amp; Markets, RIA Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,262 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Pinecone, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Synapse, MLflow, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc401ce0ff1b7af4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Kafka, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineering, Enterprise IAM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f237f0aade6c7a7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Founding Software Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Gemini, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4528f3f265ee0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce378543f6aedb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83a1d5c6d0344680</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; AI Engineer - Drilling Services</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Weatherford</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cef0d3964a633a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Supply Chain AI Enablement Intern</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pacific Gas and Electric</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b280b1bc6faa783d</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Fullstack Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BirdEye Inc India</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,812 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8a8e0919415865</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Machine Learning</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Hugging Face, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038eede1aae64fff</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Azure ML, AKS, CI/CD, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5a0c3d93e2f8974</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Azure ML, AKS, CI/CD, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0a34bf7ddf199f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Associate - AI Product Insights Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Git, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=056938708889ed60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, S3, EC2, Glue, Docker, Apache Airflow, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cross River Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fort Lee, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Docker, Kubernetes, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f3a76c8e8925cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Okta IAM Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89e35139815f4a73</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Associate Network Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ESP Enterprises</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9baceae3fe3d0259</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Copilot, S3, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba5240c71c585ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Developer IV</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RealPage Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885c0a8d0ecd2f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Developer IV</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RealPage Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d554189f2a579e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Associate - AI Solutions Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, FastAPI, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a05ce7e2e132701b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>11.1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Synapse, MLflow, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=840a0631cd9b55e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf59616c79877ad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=518fdc3a86ff73dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Engineer, Software</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NETGEAR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fe8f5a94d21723c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Intern, Hockey Research</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chicago Blackhawks</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a22cb6f11efc4f3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior .NET Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capital Markets Gateway</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Peru, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=028943326c9208b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Advanced DevOps Specialist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>General Dynamics Mission Systems</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f468939676656996</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes</t>
+          <t>RAG, S3, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Hugging Face, Prompt Engineering, S3, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=7f87a27c9594b0e3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Agentic AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=55744878dcd050aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Azure ML, AKS, CI/CD, Databricks, PySpark</t>
+          <t>RAG, Redshift, Kinesis, CI/CD, Git, Snowflake, Redshift, Kafka, Hadoop, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a0c3d93e2f8974</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Software Engineer - Contract AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Azure ML, AKS, CI/CD, Databricks, PySpark</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a34bf7ddf199f2</t>
+          <t>https://www.indeed.com/viewjob?jk=daa74a432eb3224f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Product Insights Analyst</t>
+          <t>Civil AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=056938708889ed60</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cbd17b0dd3453e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>FinOps engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, EC2, Glue, Docker, Apache Airflow, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, BigQuery, Kubernetes, Terraform, Git, BigQuery, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=8d3bcb1b4c3f993f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=f682b8e9419ea4fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Docker, Kubernetes, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f3a76c8e8925cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0c321966af99b94d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e35139815f4a73</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffee4ed2ed60143</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Network Operations Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ESP Enterprises</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, Python, R</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,427 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baceae3fe3d0259</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Copilot, S3, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba5240c71c585ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Developer IV</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>RealPage Inc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=885c0a8d0ecd2f63</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Developer IV</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>RealPage Inc</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d554189f2a579e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Associate - AI Solutions Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, FastAPI, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a05ce7e2e132701b</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=840a0631cd9b55e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf59616c79877ad8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=518fdc3a86ff73dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Engineer, Software</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NETGEAR</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe8f5a94d21723c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Intern, Hockey Research</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Chicago Blackhawks</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a22cb6f11efc4f3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior .NET Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Capital Markets Gateway</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Peru, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=028943326c9208b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Advanced DevOps Specialist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>General Dynamics Mission Systems</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f468939676656996</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, S3, Data Lake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AI Engineer, RAG, S3, EC2, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f87a27c9594b0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Agentic AI Architect</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,29 +556,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Hugging Face, TensorFlow, PyTorch, Git</t>
+          <t>AI Engineer, Data Scientist, RAG, Data Lake, Docker, Kubernetes, AKS, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55744878dcd050aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Kinesis, CI/CD, Git, Snowflake, Redshift, Kafka, Hadoop, Power BI</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Snowflake, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contract AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Python</t>
+          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Databricks, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa74a432eb3224f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Civil AI Engineer</t>
+          <t>Full Stack Laravel Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bentley Systems</t>
+          <t>Cause Strategy Partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, PyTorch, Git, Python, R</t>
+          <t>RAG, Gemini, Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cbd17b0dd3453e</t>
+          <t>https://www.indeed.com/viewjob?jk=20fb0f921574fe5a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FinOps engineer</t>
+          <t>Smart Manufacturing Software Dev Eng</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xsolla</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, Terraform, Git, BigQuery, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d3bcb1b4c3f993f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5d21394792b71b0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Junior Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SynapseMX, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>RAG, Synapse, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f682b8e9419ea4fe</t>
+          <t>https://www.indeed.com/viewjob?jk=497329d238bfcb03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
+          <t>Senior Consultant - AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>Kalles Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c321966af99b94d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8fe657fbcb328f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
+          <t>Software Developer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>RAG, FastAPI, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffee4ed2ed60143</t>
+          <t>https://www.indeed.com/viewjob?jk=8626d79e8e8f6c1d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Snowflake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,112 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Mid-Level Full Stack Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>SynapseMX, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf846bb94476b86c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist I- Enterprise Complaints Management</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hadoop, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3726801c2001974e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Intern, Hockey Research</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chicago Blackhawks</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abf303d0e8c96d0e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-21.xlsx
+++ b/daily_matches/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, S3, Data Lake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Kinesis, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7a26555a7e1695a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, EC2, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Kinesis, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=41d41dba6e5bbf64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,46 +552,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, Docker, Kubernetes, AKS, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering, Azure ML</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Sr. Software Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Snowflake, MongoDB, NoSQL, Python</t>
+          <t>RAG, PyTorch, OpenCV, MLflow, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1cc7ed01516299</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Databricks, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Snowflake, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Laravel Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cause Strategy Partners</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Copilot, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20fb0f921574fe5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Smart Manufacturing Software Dev Eng</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>AI Engineer, Generative AI, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5d21394792b71b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef196cc40e25d615</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Full Stack Developer</t>
+          <t>Machine Learning Engineer - Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SynapseMX, Inc</t>
+          <t>Data Recognition Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497329d238bfcb03</t>
+          <t>https://www.indeed.com/viewjob?jk=8857e44e29ea750b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Consultant - AI Engineer</t>
+          <t>Machine Learning Engineer - Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kalles Group</t>
+          <t>Data Recognition Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Maple Grove, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8fe657fbcb328f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9da226c099c4f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer - Virtualization and SIL Integration</t>
+          <t>Senior Platform Engineer - Infrastructure and Automation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8626d79e8e8f6c1d</t>
+          <t>https://www.indeed.com/viewjob?jk=71ea925983607ef3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Snowflake, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mid-Level Full Stack Developer</t>
+          <t>AI Full Stack Engineer (Info Retrieval, mid-career)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SynapseMX, Inc</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf846bb94476b86c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0dfa120bfe6259</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist I- Enterprise Complaints Management</t>
+          <t>Mobile SDET / Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>ProphetX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,52 +906,227 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hadoop, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3726801c2001974e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff492b435f96d43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intern, Hockey Research</t>
+          <t>Sr Software Engineer, AI Tools – Python Pipeline</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e42a858d7c98794a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abf303d0e8c96d0e</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Tableau, Quicksight, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62015460085feb62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tradeweb</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd73eea71a58ebd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wilson &amp; Company, Inc., Engineers &amp; Architects</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1382079ab104bfa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Platform/Infrastructure Eng.,Conversational AI &amp; Immersive Character</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21e2c52d78219d5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Commence</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Leesburg, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=283ce4a3e5ba2f42</t>
         </is>
       </c>
     </row>
